--- a/scratch/Ma_Bakery_Final_Financial_Statements_2025-2026.xlsx
+++ b/scratch/Ma_Bakery_Final_Financial_Statements_2025-2026.xlsx
@@ -479,7 +479,7 @@
         <v>Generated Timestamp</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-09-30T05:19:55.525Z</v>
+        <v>2026-09-30T15:40:26.597Z</v>
       </c>
     </row>
     <row r="12">
